--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-24.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -875,16 +875,16 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.82</v>
@@ -893,184 +893,184 @@
         <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
         <v>2.06</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
         <v>5.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1.46</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>1.21</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
         <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
         <v>10.5</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="I7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -2414,7 +2414,7 @@
         <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="G9" t="n">
         <v>600</v>
@@ -2650,7 +2650,7 @@
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>3.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>600</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>870</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H12" t="n">
         <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
         <v>9.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.95</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>4.8</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
         <v>3.9</v>
@@ -5190,7 +5190,7 @@
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
         <v>1.81</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H20" t="n">
         <v>2.76</v>
@@ -5444,7 +5444,7 @@
         <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5453,13 +5453,13 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.32</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>1.98</v>
@@ -5567,7 +5567,7 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
         <v>25</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H21" t="n">
         <v>6.2</v>
@@ -5698,7 +5698,7 @@
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -5949,10 +5949,10 @@
         <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
         <v>1.81</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
         <v>600</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>870</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>2.9</v>
       </c>
       <c r="H27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I27" t="n">
         <v>2.96</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
         <v>600</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
         <v>870</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G29" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
         <v>8.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
         <v>4.5</v>
@@ -7748,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
@@ -7778,7 +7778,7 @@
         <v>85</v>
       </c>
       <c r="AA29" t="n">
-        <v>340</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>8</v>
@@ -7787,7 +7787,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
@@ -7853,7 +7853,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
         <v>42</v>
@@ -7880,55 +7880,55 @@
         <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="G31" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H31" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -8734,10 +8734,10 @@
         <v>1.82</v>
       </c>
       <c r="G33" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I33" t="n">
         <v>3.85</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H34" t="n">
         <v>3.65</v>
@@ -9000,7 +9000,7 @@
         <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -9239,19 +9239,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="H35" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>140</v>
+        <v>660</v>
       </c>
       <c r="J35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H36" t="n">
         <v>1.59</v>
@@ -9505,10 +9505,10 @@
         <v>2.08</v>
       </c>
       <c r="J36" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
         <v>1.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -10001,16 +10001,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J38" t="n">
         <v>5.1</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H39" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="K39" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G40" t="n">
         <v>2.18</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>2.8</v>
       </c>
       <c r="J41" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
         <v>3.4</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -11026,13 +11026,13 @@
         <v>2.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K42" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11047,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q42" t="n">
         <v>1.94</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -11531,13 +11531,13 @@
         <v>1.84</v>
       </c>
       <c r="H44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I44" t="n">
         <v>5.4</v>
       </c>
       <c r="J44" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K44" t="n">
         <v>3.75</v>
@@ -11687,13 +11687,13 @@
         <v>44</v>
       </c>
       <c r="BH44" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI44" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ44" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK44" t="n">
         <v>1.01</v>
@@ -11705,37 +11705,37 @@
         <v>1.01</v>
       </c>
       <c r="BN44" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO44" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP44" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ44" t="n">
         <v>1.01</v>
       </c>
       <c r="BR44" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS44" t="n">
         <v>1.01</v>
       </c>
       <c r="BT44" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU44" t="n">
         <v>1.01</v>
       </c>
       <c r="BV44" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW44" t="n">
         <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G45" t="n">
         <v>6.2</v>
       </c>
       <c r="H45" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I45" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J45" t="n">
         <v>4.4</v>
@@ -11806,19 +11806,19 @@
         <v>4.7</v>
       </c>
       <c r="O45" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P45" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R45" t="n">
         <v>1.5</v>
       </c>
       <c r="S45" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T45" t="n">
         <v>1.82</v>
@@ -11836,13 +11836,13 @@
         <v>24</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z45" t="n">
         <v>10.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB45" t="n">
         <v>28</v>
@@ -11851,13 +11851,13 @@
         <v>11</v>
       </c>
       <c r="AD45" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE45" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AF45" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AG45" t="n">
         <v>23</v>
@@ -11893,22 +11893,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR45" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT45" t="n">
         <v>20</v>
       </c>
       <c r="AU45" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV45" t="n">
         <v>9</v>
       </c>
-      <c r="AV45" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW45" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX45" t="n">
         <v>26</v>
@@ -11917,7 +11917,7 @@
         <v>19.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA45" t="n">
         <v>21</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -12042,10 +12042,10 @@
         <v>12.5</v>
       </c>
       <c r="I46" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K46" t="n">
         <v>6.4</v>
@@ -12066,10 +12066,10 @@
         <v>2.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R46" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S46" t="n">
         <v>2.9</v>
@@ -12111,7 +12111,7 @@
         <v>330</v>
       </c>
       <c r="AF46" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG46" t="n">
         <v>11</v>
@@ -12150,7 +12150,7 @@
         <v>40</v>
       </c>
       <c r="AS46" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AT46" t="n">
         <v>7.6</v>
@@ -12186,7 +12186,7 @@
         <v>40</v>
       </c>
       <c r="BE46" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF46" t="n">
         <v>4.8</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
         <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R47" t="n">
         <v>1.45</v>
@@ -12350,7 +12350,7 @@
         <v>8.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB47" t="n">
         <v>27</v>
@@ -12377,7 +12377,7 @@
         <v>40</v>
       </c>
       <c r="AJ47" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
         <v>150</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G48" t="n">
         <v>13</v>
@@ -12553,7 +12553,7 @@
         <v>1.35</v>
       </c>
       <c r="J48" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K48" t="n">
         <v>6</v>
@@ -12577,7 +12577,7 @@
         <v>1.9</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
         <v>3.3</v>
@@ -12610,7 +12610,7 @@
         <v>34</v>
       </c>
       <c r="AC48" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD48" t="n">
         <v>11.5</v>
@@ -12661,7 +12661,7 @@
         <v>9</v>
       </c>
       <c r="AT48" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU48" t="n">
         <v>11.5</v>
@@ -12685,7 +12685,7 @@
         <v>28</v>
       </c>
       <c r="BB48" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BC48" t="n">
         <v>95</v>
@@ -12700,7 +12700,7 @@
         <v>55</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH48" t="n">
         <v>3.7</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H49" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="I49" t="n">
         <v>3.4</v>
@@ -12810,7 +12810,7 @@
         <v>3.1</v>
       </c>
       <c r="K49" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -12825,10 +12825,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>2.86</v>
       </c>
       <c r="I51" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>4</v>
@@ -13333,22 +13333,22 @@
         <v>1.17</v>
       </c>
       <c r="P51" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R51" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S51" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
         <v>1.49</v>
       </c>
       <c r="U51" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -13402,19 +13402,19 @@
         <v>32</v>
       </c>
       <c r="AM51" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN51" t="n">
         <v>12</v>
       </c>
       <c r="AO51" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP51" t="n">
         <v>24</v>
       </c>
       <c r="AQ51" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR51" t="n">
         <v>21</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -15081,22 +15081,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="G58" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I58" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K58" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="G61" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H61" t="n">
         <v>5.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J61" t="n">
         <v>3.35</v>
       </c>
       <c r="K61" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
         <v>3.25</v>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>2.94</v>
@@ -16623,13 +16623,13 @@
         <v>3.3</v>
       </c>
       <c r="L64" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M64" t="n">
         <v>1.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O64" t="n">
         <v>1.44</v>
@@ -16638,7 +16638,7 @@
         <v>1.67</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R64" t="n">
         <v>1.25</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -16859,22 +16859,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J65" t="n">
         <v>3.2</v>
       </c>
-      <c r="H65" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J65" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K65" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -16889,10 +16889,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
         <v>5.5</v>
       </c>
       <c r="K66" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -17370,16 +17370,16 @@
         <v>3.2</v>
       </c>
       <c r="G67" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H67" t="n">
         <v>2.5</v>
       </c>
       <c r="I67" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="J67" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K67" t="n">
         <v>3.3</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>
@@ -17908,7 +17908,7 @@
         <v>1.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-22 02:43:47</t>
+          <t>2026-05-22 05:16:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-24.xlsx
@@ -860,13 +860,13 @@
         <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
         <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1028,49 +1028,49 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>2.98</v>
@@ -1129,212 +1129,212 @@
         <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
         <v>1.64</v>
@@ -1401,184 +1401,184 @@
         <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -1619,34 +1619,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.2</v>
@@ -1655,184 +1655,184 @@
         <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -1891,16 +1891,16 @@
         <v>10.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
         <v>2.5</v>
@@ -1909,194 +1909,194 @@
         <v>1.56</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.24</v>
       </c>
       <c r="G7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
         <v>12.5</v>
@@ -2139,22 +2139,22 @@
         <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>7.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
         <v>2.44</v>
@@ -2163,194 +2163,194 @@
         <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -2393,22 +2393,22 @@
         <v>1.78</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>1.68</v>
@@ -2417,194 +2417,194 @@
         <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -2653,16 +2653,16 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
         <v>1.5</v>
@@ -2671,194 +2671,194 @@
         <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
         <v>1.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="G12" t="n">
         <v>1.89</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>4.8</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G13" t="n">
         <v>1.41</v>
@@ -3660,13 +3660,13 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G16" t="n">
         <v>1.55</v>
@@ -4422,13 +4422,13 @@
         <v>6.8</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
         <v>4.9</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
         <v>1.51</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
         <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I20" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
         <v>3.4</v>
@@ -5459,10 +5459,10 @@
         <v>1.32</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
         <v>1.38</v>
@@ -5474,7 +5474,7 @@
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA20" t="n">
         <v>46</v>
@@ -5498,7 +5498,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
         <v>12.5</v>
@@ -5510,7 +5510,7 @@
         <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>17</v>
@@ -5537,7 +5537,7 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
         <v>10.5</v>
@@ -5552,7 +5552,7 @@
         <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
@@ -5579,7 +5579,7 @@
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BE20" t="n">
         <v>36</v>
@@ -5594,19 +5594,19 @@
         <v>3.45</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN20" t="n">
         <v>5.9</v>
@@ -5618,13 +5618,13 @@
         <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR20" t="n">
         <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT20" t="n">
         <v>5.8</v>
@@ -5636,10 +5636,10 @@
         <v>21</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY20" t="n">
         <v>10.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
         <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q22" t="n">
         <v>2.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -6197,16 +6197,16 @@
         <v>3.35</v>
       </c>
       <c r="H23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J23" t="n">
         <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>1.81</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.65</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
         <v>1.79</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -7479,16 +7479,16 @@
         <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P28" t="n">
         <v>1.24</v>
@@ -7497,194 +7497,194 @@
         <v>1.01</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -7724,13 +7724,13 @@
         <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
@@ -7757,7 +7757,7 @@
         <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
         <v>1.85</v>
@@ -7784,10 +7784,10 @@
         <v>8</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
@@ -7823,7 +7823,7 @@
         <v>230</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>20</v>
@@ -7835,7 +7835,7 @@
         <v>95</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
         <v>9</v>
@@ -7871,7 +7871,7 @@
         <v>44</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG29" t="n">
         <v>46</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -8223,23 +8223,23 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K31" t="n">
         <v>5.1</v>
       </c>
-      <c r="J31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
         <v>4.3</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H33" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I33" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>4.6</v>
       </c>
       <c r="K33" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -8991,17 +8991,17 @@
         <v>2.36</v>
       </c>
       <c r="H34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K34" t="n">
         <v>3.65</v>
       </c>
-      <c r="I34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q34" t="n">
         <v>2.2</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>660</v>
+        <v>870</v>
       </c>
       <c r="J35" t="n">
         <v>4.5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G36" t="n">
         <v>600</v>
       </c>
       <c r="H36" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="I36" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
         <v>1.74</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>660</v>
+        <v>870</v>
       </c>
       <c r="J37" t="n">
         <v>4.6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>1.28</v>
       </c>
       <c r="G39" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H39" t="n">
         <v>11.5</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G40" t="n">
         <v>2.18</v>
@@ -10521,29 +10521,29 @@
         <v>6</v>
       </c>
       <c r="J40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.66</v>
       </c>
-      <c r="K40" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.74</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -10763,19 +10763,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H41" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
         <v>3.4</v>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q41" t="n">
         <v>2.1</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G42" t="n">
         <v>3.85</v>
@@ -11026,7 +11026,7 @@
         <v>2.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="J42" t="n">
         <v>3.2</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G44" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I44" t="n">
         <v>5.3</v>
       </c>
-      <c r="I44" t="n">
-        <v>5.4</v>
-      </c>
       <c r="J44" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K44" t="n">
         <v>3.75</v>
@@ -11549,19 +11549,19 @@
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O44" t="n">
         <v>1.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S44" t="n">
         <v>4.9</v>
@@ -11582,16 +11582,16 @@
         <v>10.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z44" t="n">
         <v>44</v>
       </c>
       <c r="AA44" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC44" t="n">
         <v>8.4</v>
@@ -11600,7 +11600,7 @@
         <v>23</v>
       </c>
       <c r="AE44" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF44" t="n">
         <v>9.199999999999999</v>
@@ -11624,19 +11624,19 @@
         <v>60</v>
       </c>
       <c r="AM44" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO44" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR44" t="n">
         <v>22</v>
@@ -11651,7 +11651,7 @@
         <v>7.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW44" t="n">
         <v>36</v>
@@ -11684,25 +11684,25 @@
         <v>15.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ44" t="n">
         <v>12.5</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN44" t="n">
         <v>4.3</v>
@@ -11714,31 +11714,31 @@
         <v>14</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR44" t="n">
         <v>38</v>
       </c>
       <c r="BS44" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT44" t="n">
         <v>9.4</v>
       </c>
       <c r="BU44" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV44" t="n">
         <v>65</v>
       </c>
       <c r="BW44" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX44" t="n">
         <v>80</v>
       </c>
       <c r="BY44" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G45" t="n">
         <v>6.2</v>
       </c>
       <c r="H45" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I45" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J45" t="n">
         <v>4.4</v>
@@ -11803,7 +11803,7 @@
         <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O45" t="n">
         <v>1.24</v>
@@ -11821,7 +11821,7 @@
         <v>2.84</v>
       </c>
       <c r="T45" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U45" t="n">
         <v>2.16</v>
@@ -11836,13 +11836,13 @@
         <v>24</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
         <v>10.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB45" t="n">
         <v>28</v>
@@ -11854,13 +11854,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE45" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AF45" t="n">
         <v>180</v>
       </c>
       <c r="AG45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH45" t="n">
         <v>25</v>
@@ -11872,13 +11872,13 @@
         <v>180</v>
       </c>
       <c r="AK45" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL45" t="n">
         <v>85</v>
       </c>
       <c r="AM45" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN45" t="n">
         <v>100</v>
@@ -11887,16 +11887,16 @@
         <v>7.8</v>
       </c>
       <c r="AP45" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ45" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS45" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT45" t="n">
         <v>20</v>
@@ -11917,7 +11917,7 @@
         <v>19.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA45" t="n">
         <v>21</v>
@@ -11944,55 +11944,55 @@
         <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN45" t="n">
         <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT45" t="n">
         <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -12033,22 +12033,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G46" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H46" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J46" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -12057,13 +12057,13 @@
         <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P46" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q46" t="n">
         <v>1.76</v>
@@ -12072,13 +12072,13 @@
         <v>1.5</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T46" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -12099,7 +12099,7 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC46" t="n">
         <v>13.5</v>
@@ -12108,10 +12108,10 @@
         <v>50</v>
       </c>
       <c r="AE46" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AF46" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG46" t="n">
         <v>11</v>
@@ -12120,10 +12120,10 @@
         <v>42</v>
       </c>
       <c r="AI46" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK46" t="n">
         <v>16</v>
@@ -12132,13 +12132,13 @@
         <v>55</v>
       </c>
       <c r="AM46" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN46" t="n">
         <v>5.2</v>
       </c>
       <c r="AO46" t="n">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AP46" t="n">
         <v>17.5</v>
@@ -12153,13 +12153,13 @@
         <v>110</v>
       </c>
       <c r="AT46" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU46" t="n">
         <v>12</v>
       </c>
       <c r="AV46" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW46" t="n">
         <v>95</v>
@@ -12171,10 +12171,10 @@
         <v>10</v>
       </c>
       <c r="AZ46" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BA46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB46" t="n">
         <v>9</v>
@@ -12183,13 +12183,13 @@
         <v>13.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BE46" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF46" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG46" t="n">
         <v>95</v>
@@ -12198,55 +12198,55 @@
         <v>1000</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN46" t="n">
         <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -12287,16 +12287,16 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G47" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G47" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="H47" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="J47" t="n">
         <v>4.9</v>
@@ -12311,16 +12311,16 @@
         <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R47" t="n">
         <v>1.45</v>
@@ -12329,10 +12329,10 @@
         <v>3.05</v>
       </c>
       <c r="T47" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -12341,46 +12341,46 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD47" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE47" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF47" t="n">
         <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH47" t="n">
         <v>27</v>
       </c>
       <c r="AI47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ47" t="n">
         <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
@@ -12392,13 +12392,13 @@
         <v>210</v>
       </c>
       <c r="AO47" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AP47" t="n">
         <v>16</v>
       </c>
       <c r="AQ47" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR47" t="n">
         <v>7.8</v>
@@ -12407,7 +12407,7 @@
         <v>11</v>
       </c>
       <c r="AT47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU47" t="n">
         <v>10</v>
@@ -12416,28 +12416,28 @@
         <v>9.6</v>
       </c>
       <c r="AW47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX47" t="n">
         <v>32</v>
       </c>
       <c r="AY47" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ47" t="n">
         <v>23</v>
       </c>
       <c r="BA47" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB47" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BC47" t="n">
         <v>42</v>
       </c>
       <c r="BD47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE47" t="n">
         <v>44</v>
@@ -12446,61 +12446,61 @@
         <v>46</v>
       </c>
       <c r="BG47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
       </c>
       <c r="BI47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ47" t="n">
         <v>1000</v>
       </c>
       <c r="BK47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN47" t="n">
         <v>1000</v>
       </c>
       <c r="BO47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP47" t="n">
         <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR47" t="n">
         <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT47" t="n">
         <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ47" t="n">
         <v>0</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H48" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I48" t="n">
         <v>1.35</v>
@@ -12556,7 +12556,7 @@
         <v>5.8</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -12568,16 +12568,16 @@
         <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P48" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q48" t="n">
         <v>1.9</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
         <v>3.3</v>
@@ -12595,13 +12595,13 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
         <v>7.4</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="n">
         <v>10</v>
@@ -12610,7 +12610,7 @@
         <v>34</v>
       </c>
       <c r="AC48" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD48" t="n">
         <v>11.5</v>
@@ -12628,13 +12628,13 @@
         <v>46</v>
       </c>
       <c r="AI48" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ48" t="n">
         <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AL48" t="n">
         <v>1000</v>
@@ -12646,13 +12646,13 @@
         <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP48" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR48" t="n">
         <v>6.4</v>
@@ -12670,7 +12670,7 @@
         <v>10</v>
       </c>
       <c r="AW48" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX48" t="n">
         <v>38</v>
@@ -12703,7 +12703,7 @@
         <v>5.9</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI48" t="n">
         <v>3.05</v>
@@ -12712,13 +12712,13 @@
         <v>14</v>
       </c>
       <c r="BK48" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN48" t="n">
         <v>15.5</v>
@@ -12736,13 +12736,13 @@
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT48" t="n">
         <v>3.55</v>
       </c>
       <c r="BU48" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BV48" t="n">
         <v>7.6</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -12795,19 +12795,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G49" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H49" t="n">
         <v>2.74</v>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K49" t="n">
         <v>4</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G51" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H51" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J51" t="n">
         <v>4</v>
@@ -13336,7 +13336,7 @@
         <v>2.76</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R51" t="n">
         <v>1.72</v>
@@ -13378,13 +13378,13 @@
         <v>13.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF51" t="n">
         <v>22</v>
       </c>
       <c r="AG51" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH51" t="n">
         <v>14.5</v>
@@ -13393,7 +13393,7 @@
         <v>32</v>
       </c>
       <c r="AJ51" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AK51" t="n">
         <v>24</v>
@@ -13402,7 +13402,7 @@
         <v>32</v>
       </c>
       <c r="AM51" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN51" t="n">
         <v>12</v>
@@ -13414,7 +13414,7 @@
         <v>24</v>
       </c>
       <c r="AQ51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR51" t="n">
         <v>21</v>
@@ -13435,7 +13435,7 @@
         <v>22</v>
       </c>
       <c r="AX51" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY51" t="n">
         <v>11</v>
@@ -13468,65 +13468,65 @@
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -15081,22 +15081,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="G58" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H58" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K58" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>1.49</v>
       </c>
       <c r="G60" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H60" t="n">
         <v>6.2</v>
@@ -15622,7 +15622,7 @@
         <v>2.48</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G61" t="n">
         <v>1.88</v>
@@ -15852,13 +15852,13 @@
         <v>5.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K61" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -16351,13 +16351,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G63" t="n">
         <v>3.85</v>
       </c>
       <c r="H63" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I63" t="n">
         <v>2.64</v>
@@ -16366,7 +16366,7 @@
         <v>3.15</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -16608,16 +16608,16 @@
         <v>2.48</v>
       </c>
       <c r="G64" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H64" t="n">
         <v>3.25</v>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K64" t="n">
         <v>3.3</v>
@@ -16638,7 +16638,7 @@
         <v>1.67</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R64" t="n">
         <v>1.25</v>
@@ -16653,10 +16653,10 @@
         <v>1.92</v>
       </c>
       <c r="V64" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W64" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X64" t="n">
         <v>12</v>
@@ -16695,7 +16695,7 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK64" t="n">
         <v>38</v>
@@ -16731,7 +16731,7 @@
         <v>3.2</v>
       </c>
       <c r="AV64" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AW64" t="n">
         <v>4.7</v>
@@ -16740,7 +16740,7 @@
         <v>4</v>
       </c>
       <c r="AY64" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AZ64" t="n">
         <v>4.2</v>
@@ -16755,7 +16755,7 @@
         <v>4.5</v>
       </c>
       <c r="BD64" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE64" t="n">
         <v>5</v>
@@ -16770,19 +16770,19 @@
         <v>2.96</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BN64" t="n">
         <v>1000</v>
@@ -16794,41 +16794,41 @@
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BT64" t="n">
         <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ64" t="n">
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
         <v>1.44</v>
       </c>
       <c r="G66" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H66" t="n">
         <v>7</v>
@@ -17128,7 +17128,7 @@
         <v>5.5</v>
       </c>
       <c r="K66" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17176,19 +17176,19 @@
         <v>75</v>
       </c>
       <c r="AA66" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB66" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC66" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD66" t="n">
         <v>32</v>
       </c>
       <c r="AE66" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF66" t="n">
         <v>14</v>
@@ -17197,7 +17197,7 @@
         <v>13</v>
       </c>
       <c r="AH66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI66" t="n">
         <v>65</v>
@@ -17221,43 +17221,43 @@
         <v>55</v>
       </c>
       <c r="AP66" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ66" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR66" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS66" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT66" t="n">
         <v>12.5</v>
       </c>
       <c r="AU66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV66" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW66" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX66" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY66" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ66" t="n">
         <v>16</v>
       </c>
       <c r="BA66" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB66" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC66" t="n">
         <v>10.5</v>
@@ -17266,13 +17266,13 @@
         <v>18</v>
       </c>
       <c r="BE66" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF66" t="n">
         <v>3.65</v>
       </c>
       <c r="BG66" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -17370,13 +17370,13 @@
         <v>3.2</v>
       </c>
       <c r="G67" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H67" t="n">
         <v>2.5</v>
       </c>
       <c r="I67" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>2.92</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -17624,19 +17624,19 @@
         <v>2.02</v>
       </c>
       <c r="G68" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H68" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J68" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K68" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -17654,7 +17654,7 @@
         <v>1.77</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
         <v>2.28</v>
       </c>
       <c r="G69" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H69" t="n">
         <v>3.5</v>
@@ -17908,7 +17908,7 @@
         <v>1.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-22 05:16:15</t>
+          <t>2026-05-22 07:49:45</t>
         </is>
       </c>
     </row>
